--- a/Data/Output/ReporteClientesProcesados16082025.xlsx
+++ b/Data/Output/ReporteClientesProcesados16082025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\UiPath\Uipath_RPA_EstebanGarnica\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA04E5FE-49A0-48DD-BE7A-394C1547646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946CD96C-6241-48EF-8649-951BB1825D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{312246DE-1E2C-44D0-ABE0-913FEA36CBC1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AAEB5EED-0BFB-4C1E-9C36-305555D156C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>IDENTIFICACION</t>
   </si>
@@ -66,6 +66,9 @@
     <t>ESTADO</t>
   </si>
   <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
     <t>CEDULA</t>
   </si>
   <si>
@@ -84,19 +87,43 @@
     <t>pedroguevara@hotmail.com</t>
   </si>
   <si>
+    <t>Procesado</t>
+  </si>
+  <si>
+    <t>CARRIÓN</t>
+  </si>
+  <si>
+    <t>LEONARDO</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>leo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Cédula</t>
+  </si>
+  <si>
+    <t>garnica_esteban@hotmail.com</t>
+  </si>
+  <si>
+    <t>Pizanán</t>
+  </si>
+  <si>
+    <t>Joselin</t>
+  </si>
+  <si>
+    <t>Buñay</t>
+  </si>
+  <si>
+    <t>Tatiana</t>
+  </si>
+  <si>
+    <t>NO DISPONIBLE</t>
+  </si>
+  <si>
     <t>Cargado</t>
-  </si>
-  <si>
-    <t>CARRIÓN</t>
-  </si>
-  <si>
-    <t>LEONARDO</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>leo@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -468,11 +495,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4727F97-154E-4D2C-A1EB-091EEE5C51F1}">
-  <dimension ref="A1:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12712B31-3979-439C-A9EC-FFC4B0F71119}">
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,63 +527,182 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1723456701</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1">
         <v>45885</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1700052315</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1">
         <v>45885</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1723922801</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45885</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>401794425</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1">
+        <v>45885</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1717430100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1">
+        <v>45885</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45885</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +711,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{266E468F-53A8-4255-AEAD-92B1373538B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D511B8-D5BD-46AE-9C20-689CA883C181}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
